--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/16,09,26 Останкино СЫРЫ/дв 16,09,26 лгрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/16,09,26 Останкино СЫРЫ/дв 16,09,26 лгрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\16,09,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA000B7-0324-45EE-BCFB-764CC3410DB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622E15E7-B341-49C4-B7AE-CC0BC995687E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,20 +22,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AI$42</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="91">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -306,6 +298,9 @@
   <si>
     <t>заказ</t>
   </si>
+  <si>
+    <t>21,09,</t>
+  </si>
 </sst>
 </file>
 
@@ -423,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -438,11 +433,9 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -462,7 +455,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -2473,7 +2466,9 @@
       </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
+      <c r="T4" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
@@ -2695,7 +2690,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="5"/>
-      <c r="U6" s="14"/>
+      <c r="U6" s="1"/>
       <c r="V6" s="1">
         <f>(F6+O6+P6+S6)/Q6</f>
         <v>17.8125</v>
@@ -2809,7 +2804,7 @@
         <f>VLOOKUP(A7,заказ!A:B,2,0)</f>
         <v>24</v>
       </c>
-      <c r="U7" s="14"/>
+      <c r="U7" s="1"/>
       <c r="V7" s="1">
         <f>(F7+O7+P7+S7)/Q7</f>
         <v>14</v>
@@ -2917,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="5"/>
-      <c r="U8" s="14"/>
+      <c r="U8" s="1"/>
       <c r="V8" s="1">
         <f t="shared" ref="V8:V42" si="8">(F8+O8+P8+S8)/Q8</f>
         <v>25.384615384615383</v>
@@ -3034,7 +3029,7 @@
         <f>VLOOKUP(A9,заказ!A:B,2,0)</f>
         <v>170</v>
       </c>
-      <c r="U9" s="14">
+      <c r="U9" s="1">
         <f>VLOOKUP(A9,[1]Sheet!$A:$S,19,0)</f>
         <v>170</v>
       </c>
@@ -3100,40 +3095,40 @@
       <c r="AX9" s="1"/>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="16">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15">
         <v>0</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <v>180</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15">
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15">
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="14">
         <v>0</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="16">
         <v>0</v>
       </c>
       <c r="S10" s="5">
@@ -3141,52 +3136,52 @@
         <v>0</v>
       </c>
       <c r="T10" s="5"/>
-      <c r="U10" s="18">
+      <c r="U10" s="14">
         <f>VLOOKUP(A10,[1]Sheet!$A:$S,19,0)</f>
         <v>0</v>
       </c>
-      <c r="V10" s="15" t="e">
+      <c r="V10" s="14" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W10" s="15" t="e">
+      <c r="W10" s="14" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X10" s="15">
+      <c r="X10" s="14">
         <v>0</v>
       </c>
-      <c r="Y10" s="15">
+      <c r="Y10" s="14">
         <v>0</v>
       </c>
-      <c r="Z10" s="15">
+      <c r="Z10" s="14">
         <v>0</v>
       </c>
-      <c r="AA10" s="15">
+      <c r="AA10" s="14">
         <v>0</v>
       </c>
-      <c r="AB10" s="15">
+      <c r="AB10" s="14">
         <v>0.4</v>
       </c>
-      <c r="AC10" s="15">
+      <c r="AC10" s="14">
         <v>-0.6</v>
       </c>
-      <c r="AD10" s="15">
+      <c r="AD10" s="14">
         <v>2.4</v>
       </c>
-      <c r="AE10" s="15">
+      <c r="AE10" s="14">
         <v>4.5999999999999996</v>
       </c>
-      <c r="AF10" s="15">
+      <c r="AF10" s="14">
         <v>0</v>
       </c>
-      <c r="AG10" s="15">
+      <c r="AG10" s="14">
         <v>0</v>
       </c>
-      <c r="AH10" s="15" t="s">
+      <c r="AH10" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="AI10" s="15">
+      <c r="AI10" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3207,40 +3202,40 @@
       <c r="AX10" s="1"/>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="16">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15">
         <v>0</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="14">
         <v>180</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15">
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15">
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="14">
         <v>0</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R11" s="17">
+      <c r="R11" s="16">
         <v>0</v>
       </c>
       <c r="S11" s="5">
@@ -3248,52 +3243,52 @@
         <v>0</v>
       </c>
       <c r="T11" s="5"/>
-      <c r="U11" s="18">
+      <c r="U11" s="14">
         <f>VLOOKUP(A11,[1]Sheet!$A:$S,19,0)</f>
         <v>0</v>
       </c>
-      <c r="V11" s="15" t="e">
+      <c r="V11" s="14" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W11" s="15" t="e">
+      <c r="W11" s="14" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X11" s="15">
+      <c r="X11" s="14">
         <v>0</v>
       </c>
-      <c r="Y11" s="15">
+      <c r="Y11" s="14">
         <v>0</v>
       </c>
-      <c r="Z11" s="15">
+      <c r="Z11" s="14">
         <v>0</v>
       </c>
-      <c r="AA11" s="15">
+      <c r="AA11" s="14">
         <v>0</v>
       </c>
-      <c r="AB11" s="15">
+      <c r="AB11" s="14">
         <v>0</v>
       </c>
-      <c r="AC11" s="15">
+      <c r="AC11" s="14">
         <v>-0.8</v>
       </c>
-      <c r="AD11" s="15">
+      <c r="AD11" s="14">
         <v>0.8</v>
       </c>
-      <c r="AE11" s="15">
+      <c r="AE11" s="14">
         <v>5.6</v>
       </c>
-      <c r="AF11" s="15">
+      <c r="AF11" s="14">
         <v>0</v>
       </c>
-      <c r="AG11" s="15">
+      <c r="AG11" s="14">
         <v>0</v>
       </c>
-      <c r="AH11" s="15" t="s">
+      <c r="AH11" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="AI11" s="15">
+      <c r="AI11" s="14">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
@@ -3365,7 +3360,7 @@
         <f>VLOOKUP(A12,заказ!A:B,2,0)</f>
         <v>66</v>
       </c>
-      <c r="U12" s="14"/>
+      <c r="U12" s="1"/>
       <c r="V12" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -3471,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="5"/>
-      <c r="U13" s="14"/>
+      <c r="U13" s="1"/>
       <c r="V13" s="1">
         <f t="shared" si="8"/>
         <v>95</v>
@@ -3585,7 +3580,7 @@
         <f>VLOOKUP(A14,заказ!A:B,2,0)</f>
         <v>300</v>
       </c>
-      <c r="U14" s="14">
+      <c r="U14" s="1">
         <f>VLOOKUP(A14,[1]Sheet!$A:$S,19,0)</f>
         <v>300</v>
       </c>
@@ -3694,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="5"/>
-      <c r="U15" s="14"/>
+      <c r="U15" s="1"/>
       <c r="V15" s="1">
         <f t="shared" si="8"/>
         <v>25.000000000000004</v>
@@ -3811,7 +3806,7 @@
         <f>VLOOKUP(A16,заказ!A:B,2,0)</f>
         <v>204</v>
       </c>
-      <c r="U16" s="14">
+      <c r="U16" s="1">
         <f>VLOOKUP(A16,[1]Sheet!$A:$S,19,0)</f>
         <v>200</v>
       </c>
@@ -3928,7 +3923,7 @@
         <f>VLOOKUP(A17,заказ!A:B,2,0)</f>
         <v>192</v>
       </c>
-      <c r="U17" s="14"/>
+      <c r="U17" s="1"/>
       <c r="V17" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -4038,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="5"/>
-      <c r="U18" s="14">
+      <c r="U18" s="1">
         <f>VLOOKUP(A18,[1]Sheet!$A:$S,19,0)</f>
         <v>50</v>
       </c>
@@ -4153,7 +4148,7 @@
         <f>VLOOKUP(A19,заказ!A:B,2,0)</f>
         <v>270</v>
       </c>
-      <c r="U19" s="14"/>
+      <c r="U19" s="1"/>
       <c r="V19" s="1">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -4264,7 +4259,7 @@
         <f>VLOOKUP(A20,заказ!A:B,2,0)</f>
         <v>180</v>
       </c>
-      <c r="U20" s="14">
+      <c r="U20" s="1">
         <f>VLOOKUP(A20,[1]Sheet!$A:$S,19,0)</f>
         <v>180</v>
       </c>
@@ -4371,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="5"/>
-      <c r="U21" s="14"/>
+      <c r="U21" s="1"/>
       <c r="V21" s="1" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
@@ -4479,7 +4474,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="5"/>
-      <c r="U22" s="14"/>
+      <c r="U22" s="1"/>
       <c r="V22" s="1">
         <f t="shared" si="8"/>
         <v>105</v>
@@ -4594,7 +4589,7 @@
         <f>VLOOKUP(A23,заказ!A:B,2,0)</f>
         <v>60</v>
       </c>
-      <c r="U23" s="14">
+      <c r="U23" s="1">
         <f>VLOOKUP(A23,[1]Sheet!$A:$S,19,0)</f>
         <v>60</v>
       </c>
@@ -4713,7 +4708,7 @@
         <f>VLOOKUP(A24,заказ!A:B,2,0)</f>
         <v>48</v>
       </c>
-      <c r="U24" s="14"/>
+      <c r="U24" s="1"/>
       <c r="V24" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -4829,7 +4824,7 @@
         <f>VLOOKUP(A25,заказ!A:B,2,0)</f>
         <v>140</v>
       </c>
-      <c r="U25" s="14"/>
+      <c r="U25" s="1"/>
       <c r="V25" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -4943,7 +4938,7 @@
         <f>VLOOKUP(A26,заказ!A:B,2,0)</f>
         <v>50</v>
       </c>
-      <c r="U26" s="14">
+      <c r="U26" s="1">
         <f>VLOOKUP(A26,[1]Sheet!$A:$S,19,0)</f>
         <v>100</v>
       </c>
@@ -5056,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="T27" s="5"/>
-      <c r="U27" s="14"/>
+      <c r="U27" s="1"/>
       <c r="V27" s="1">
         <f t="shared" si="8"/>
         <v>97.5</v>
@@ -5164,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="T28" s="5"/>
-      <c r="U28" s="14"/>
+      <c r="U28" s="1"/>
       <c r="V28" s="1">
         <f t="shared" si="8"/>
         <v>14.2</v>
@@ -5280,7 +5275,7 @@
         <f>VLOOKUP(A29,заказ!A:B,2,0)</f>
         <v>200</v>
       </c>
-      <c r="U29" s="14"/>
+      <c r="U29" s="1"/>
       <c r="V29" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -5393,7 +5388,7 @@
         <f>VLOOKUP(A30,заказ!A:B,2,0)</f>
         <v>60</v>
       </c>
-      <c r="U30" s="14">
+      <c r="U30" s="1">
         <f>VLOOKUP(A30,[1]Sheet!$A:$S,19,0)</f>
         <v>60</v>
       </c>
@@ -5496,7 +5491,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="5"/>
-      <c r="U31" s="14">
+      <c r="U31" s="1">
         <f>VLOOKUP(A31,[1]Sheet!$A:$S,19,0)</f>
         <v>10</v>
       </c>
@@ -5609,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="5"/>
-      <c r="U32" s="14"/>
+      <c r="U32" s="1"/>
       <c r="V32" s="1">
         <f t="shared" si="8"/>
         <v>32.142857142857146</v>
@@ -5719,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="5"/>
-      <c r="U33" s="14"/>
+      <c r="U33" s="1"/>
       <c r="V33" s="1">
         <f t="shared" si="8"/>
         <v>36.470588235294116</v>
@@ -5829,7 +5824,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="5"/>
-      <c r="U34" s="14"/>
+      <c r="U34" s="1"/>
       <c r="V34" s="1">
         <f t="shared" si="8"/>
         <v>16.527520098948667</v>
@@ -5944,7 +5939,7 @@
         <f>VLOOKUP(A35,заказ!A:B,2,0)</f>
         <v>33</v>
       </c>
-      <c r="U35" s="14">
+      <c r="U35" s="1">
         <f>VLOOKUP(A35,[1]Sheet!$A:$S,19,0)</f>
         <v>30</v>
       </c>
@@ -6055,7 +6050,7 @@
         <f>VLOOKUP(A36,заказ!A:B,2,0)</f>
         <v>18</v>
       </c>
-      <c r="U36" s="14">
+      <c r="U36" s="1">
         <f>VLOOKUP(A36,[1]Sheet!$A:$S,19,0)</f>
         <v>40</v>
       </c>
@@ -6164,7 +6159,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="5"/>
-      <c r="U37" s="14"/>
+      <c r="U37" s="1"/>
       <c r="V37" s="1">
         <f t="shared" si="8"/>
         <v>20.68181818181818</v>
@@ -6274,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="5"/>
-      <c r="U38" s="14"/>
+      <c r="U38" s="1"/>
       <c r="V38" s="1">
         <f t="shared" si="8"/>
         <v>49.999999999999993</v>
@@ -6390,7 +6385,7 @@
         <f>VLOOKUP(A39,заказ!A:B,2,0)</f>
         <v>230</v>
       </c>
-      <c r="U39" s="14"/>
+      <c r="U39" s="1"/>
       <c r="V39" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -6496,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="5"/>
-      <c r="U40" s="14"/>
+      <c r="U40" s="1"/>
       <c r="V40" s="1">
         <f t="shared" si="8"/>
         <v>13.136792452830187</v>
@@ -6612,7 +6607,7 @@
         <f>VLOOKUP(A41,заказ!A:B,2,0)</f>
         <v>120</v>
       </c>
-      <c r="U41" s="14"/>
+      <c r="U41" s="1"/>
       <c r="V41" s="1">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -6716,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="5"/>
-      <c r="U42" s="14"/>
+      <c r="U42" s="1"/>
       <c r="V42" s="1" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
